--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513666_FASEFINALBFFB4_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513666_FASEFINALBFFB4_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7576</v>
+        <v>2.0112</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2012</v>
+        <v>3.7751</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4436</v>
+        <v>-1.7639</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0822</v>
+        <v>1.8248</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2461</v>
+        <v>2.3487</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1639</v>
+        <v>-0.5239</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0768</v>
+        <v>4.1892</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9552</v>
+        <v>3.3381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1216</v>
+        <v>0.8511</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0054</v>
+        <v>-2.3644</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2909</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2855</v>
+        <v>-1.3749</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1684</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0076</v>
+        <v>0.1553</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2081</v>
+        <v>-0.083</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2006</v>
+        <v>0.2383</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.5005</v>
+        <v>-2.1111</v>
       </c>
       <c r="W2" t="n">
-        <v>0.89</v>
+        <v>-0.3311</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3905</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1557</v>
+        <v>1.7014</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6136</v>
+        <v>2.2285</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4579</v>
+        <v>-0.5271</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8248</v>
+        <v>2.0822</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3487</v>
+        <v>2.2461</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5239</v>
+        <v>-0.1639</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1892</v>
+        <v>2.0768</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3381</v>
+        <v>1.9552</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8511</v>
+        <v>0.1216</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3644</v>
+        <v>0.0054</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9893999999999999</v>
+        <v>0.2909</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3749</v>
+        <v>-0.2855</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1421</v>
+        <v>1.1684</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
         <v>2.1421</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2999</v>
+        <v>-0.0487</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2446</v>
+        <v>0.2354</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5444</v>
+        <v>-0.284</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1111</v>
+        <v>-1.5005</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3311</v>
+        <v>0.89</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.78</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9325</v>
+        <v>1.2927</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6879</v>
+        <v>-0.3199</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7554</v>
+        <v>1.6126</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2365</v>
+        <v>2.5183</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2874</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5239</v>
+        <v>3.0329</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5812</v>
+        <v>2.4721</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1008</v>
+        <v>-1.2647</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4805</v>
+        <v>3.7368</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3447</v>
+        <v>0.0462</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3881</v>
+        <v>0.7501</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9565</v>
+        <v>-0.7039</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3895</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9474</v>
+        <v>-2.921</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5579</v>
+        <v>2.3368</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8562</v>
+        <v>-0.6414</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5565</v>
+        <v>-0.1504</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2997</v>
+        <v>-0.491</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9416</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6105</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3311</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9202</v>
+        <v>1.2771</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5810999999999999</v>
+        <v>1.9491</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5013</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5183</v>
+        <v>1.2365</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.2874</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0329</v>
+        <v>1.5239</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4721</v>
+        <v>3.5812</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2647</v>
+        <v>1.1008</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7368</v>
+        <v>2.4805</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0462</v>
+        <v>-2.3447</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7501</v>
+        <v>-1.3881</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7039</v>
+        <v>-0.9565</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.921</v>
+        <v>-1.9474</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3368</v>
+        <v>1.5579</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0139</v>
+        <v>-0.5115</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4116</v>
+        <v>-0.2953</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.2162</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.9416</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2795</v>
+        <v>0.6105</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2795</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7579</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4327</v>
+        <v>1.1347</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1906</v>
+        <v>-2.0465</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4787</v>
+        <v>1.5875</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8453</v>
+        <v>1.9427</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3666</v>
+        <v>-0.3552</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3866</v>
+        <v>2.9532</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9295</v>
+        <v>2.7505</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5429</v>
+        <v>0.2026</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-1.3657</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0842</v>
+        <v>-0.8078</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8236</v>
+        <v>-0.5578</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7789</v>
+        <v>1.7526</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7789</v>
+        <v>2.7263</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4266</v>
+        <v>-1.1993</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0462</v>
+        <v>-0.1827</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3804</v>
+        <v>-1.0166</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4421</v>
+        <v>-3.0526</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4421</v>
+        <v>-2.3905</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2643</v>
+        <v>-1.2331</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9492</v>
+        <v>1.1337</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2135</v>
+        <v>-2.3668</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5875</v>
+        <v>0.4787</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9427</v>
+        <v>1.8453</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3552</v>
+        <v>-1.3666</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9532</v>
+        <v>1.3866</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7505</v>
+        <v>1.9295</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2026</v>
+        <v>-0.5429</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3657</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8078</v>
+        <v>-0.0842</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5578</v>
+        <v>-0.8236</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7526</v>
+        <v>0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7263</v>
+        <v>0.7789</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5518</v>
+        <v>-0.0487</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3682</v>
+        <v>-0.2529</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1836</v>
+        <v>0.2042</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.0526</v>
+        <v>-2.4421</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.3905</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5048</v>
+        <v>-1.5967</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0184</v>
+        <v>-1.1937</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4865</v>
+        <v>-0.403</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6063</v>
@@ -1078,13 +1078,13 @@
         <v>1.9474</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4575</v>
+        <v>-0.5494</v>
       </c>
       <c r="T8" t="n">
-        <v>0.108</v>
+        <v>-0.0674</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5655</v>
+        <v>-0.482</v>
       </c>
       <c r="V8" t="n">
         <v>0.5590000000000001</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9202</v>
+        <v>-2.3753</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.8484</v>
+        <v>0.3722</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9282</v>
+        <v>-2.7476</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1644</v>
+        <v>-2.0693</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4706</v>
+        <v>-1.9525</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6937</v>
+        <v>-0.1168</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8001</v>
+        <v>0.5596</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5444</v>
+        <v>-0.1538</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2557</v>
+        <v>0.7134</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3643</v>
+        <v>-2.6289</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0738</v>
+        <v>-1.7987</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4381</v>
+        <v>-0.8302</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3632</v>
+        <v>2.5316</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3105</v>
+        <v>2.5316</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0743</v>
+        <v>-0.1161</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0563</v>
+        <v>-0.1873</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.018</v>
+        <v>0.0713</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0447</v>
+        <v>-2.7216</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.0447</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.397</v>
+        <v>-3.135</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2876</v>
+        <v>-5.9241</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1093</v>
+        <v>2.7891</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0693</v>
+        <v>-3.1644</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9525</v>
+        <v>-1.4706</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1168</v>
+        <v>-1.6937</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5596</v>
+        <v>-2.8001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1538</v>
+        <v>-1.5444</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7134</v>
+        <v>-1.2557</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6289</v>
+        <v>-0.3643</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7987</v>
+        <v>0.0738</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8302</v>
+        <v>-0.4381</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5316</v>
+        <v>1.3632</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5316</v>
+        <v>3.3105</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1377</v>
+        <v>-0.2891</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8472</v>
+        <v>-0.1319</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2904</v>
+        <v>-0.1572</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7216</v>
+        <v>-1.0447</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.0447</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7216</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4237</v>
+        <v>-3.5582</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.9002</v>
+        <v>-6.9791</v>
       </c>
       <c r="F11" t="n">
-        <v>3.4765</v>
+        <v>3.4209</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0463</v>
@@ -1312,13 +1312,13 @@
         <v>2.921</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7279</v>
+        <v>-0.8625</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3234</v>
+        <v>-0.4024</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4044</v>
+        <v>-0.4601</v>
       </c>
       <c r="V11" t="n">
         <v>1.3242</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.501899999999999</v>
+        <v>-6.527700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.751099999999999</v>
+        <v>-3.823499999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.750799999999999</v>
+        <v>-2.7042</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1583000000000001</v>
+        <v>-0.1583000000000014</v>
       </c>
       <c r="H12" t="n">
-        <v>2.532600000000001</v>
+        <v>2.5326</v>
       </c>
       <c r="I12" t="n">
         <v>-2.6908</v>
@@ -1366,7 +1366,7 @@
         <v>11.9986</v>
       </c>
       <c r="K12" t="n">
-        <v>7.051699999999999</v>
+        <v>7.051700000000001</v>
       </c>
       <c r="L12" t="n">
         <v>4.9468</v>
@@ -1390,13 +1390,13 @@
         <v>22.3946</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.085199999999999</v>
+        <v>-4.1114</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4455</v>
+        <v>-1.5179</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.639699999999999</v>
+        <v>-2.5933</v>
       </c>
       <c r="V12" t="n">
         <v>-10.0478</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3051</v>
+        <v>6.6033</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1586</v>
+        <v>5.3579</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1465</v>
+        <v>1.2454</v>
       </c>
       <c r="G13" t="n">
         <v>2.7751</v>
@@ -1468,13 +1468,13 @@
         <v>1.5579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8347</v>
+        <v>1.1329</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4726</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3621</v>
+        <v>0.461</v>
       </c>
       <c r="V13" t="n">
         <v>2.1111</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9639</v>
+        <v>1.8925</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6633</v>
+        <v>2.676</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6994</v>
+        <v>-0.7835</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0509</v>
+        <v>2.1487</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3948</v>
+        <v>0.3382</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3439</v>
+        <v>1.8106</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4415</v>
+        <v>3.6118</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2144</v>
+        <v>0.9776</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2271</v>
+        <v>2.6342</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3906</v>
+        <v>-1.4631</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8196</v>
+        <v>-0.6394</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.571</v>
+        <v>-0.8236</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7789</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9474</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1684</v>
+        <v>0.3895</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4125</v>
+        <v>-0.302</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6687</v>
+        <v>-0.2095</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2561</v>
+        <v>-0.0925</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2795</v>
+        <v>1.6037</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5005</v>
+        <v>1.2211</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2211</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7093</v>
+        <v>1.8402</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5763</v>
+        <v>-0.1913</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.867</v>
+        <v>2.0315</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1487</v>
+        <v>1.6001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3382</v>
+        <v>0.5285</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8106</v>
+        <v>1.0716</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6118</v>
+        <v>2.271</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9776</v>
+        <v>1.0468</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6342</v>
+        <v>1.2241</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4631</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6394</v>
+        <v>-0.5184</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8236</v>
+        <v>-0.1526</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5579</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9474</v>
+        <v>-2.921</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3895</v>
+        <v>0.9737</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4852</v>
+        <v>1.5254</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3092</v>
+        <v>0.4587</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.176</v>
+        <v>1.0667</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6037</v>
+        <v>0.6621</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3826</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.647</v>
+        <v>1.4905</v>
       </c>
       <c r="E17" t="n">
-        <v>0.008</v>
+        <v>-2.0042</v>
       </c>
       <c r="F17" t="n">
-        <v>1.639</v>
+        <v>3.4947</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6001</v>
+        <v>0.8461</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5285</v>
+        <v>-0.0842</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0716</v>
+        <v>0.9303</v>
       </c>
       <c r="J17" t="n">
-        <v>2.271</v>
+        <v>0.8051</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0468</v>
+        <v>-0.5567</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2241</v>
+        <v>1.3618</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6709000000000001</v>
+        <v>0.041</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5184</v>
+        <v>0.4725</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1526</v>
+        <v>-0.4315</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.9474</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.921</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9737</v>
+        <v>2.3368</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3322</v>
+        <v>0.5664</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6581</v>
+        <v>0.1117</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6742</v>
+        <v>0.4548</v>
       </c>
       <c r="V17" t="n">
         <v>0.6621</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3548</v>
+        <v>1.4113</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6911</v>
+        <v>0.3921</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6637</v>
+        <v>1.0192</v>
       </c>
       <c r="G18" t="n">
         <v>0.794</v>
@@ -1858,13 +1858,13 @@
         <v>1.1684</v>
       </c>
       <c r="S18" t="n">
-        <v>0.034</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3553</v>
+        <v>0.0563</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3214</v>
+        <v>0.0341</v>
       </c>
       <c r="V18" t="n">
         <v>1.5005</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2237</v>
+        <v>1.4053</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2237</v>
+        <v>2.5669</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.1615</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2237</v>
+        <v>1.0509</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6158</v>
+        <v>1.3948</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6079</v>
+        <v>-0.3439</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2237</v>
+        <v>2.4415</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6158</v>
+        <v>2.2144</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6079</v>
+        <v>0.2271</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-1.3906</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.8196</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.571</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.1684</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.8539</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.5722</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2817</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9087</v>
+        <v>1.2237</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06469999999999999</v>
+        <v>1.2237</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8439</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1817</v>
+        <v>1.2237</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5851</v>
+        <v>0.6158</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5966</v>
+        <v>0.6079</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7793</v>
+        <v>1.2237</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6207</v>
+        <v>0.6158</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1585</v>
+        <v>0.6079</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4024</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9644</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4381</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9737</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1421</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9472</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5635</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3837</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1695</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.449</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6158</v>
+        <v>0.6993</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6158</v>
+        <v>-0.633</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.3323</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6158</v>
+        <v>-3.1817</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6158</v>
+        <v>-1.5851</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-1.5966</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6158</v>
+        <v>-1.7793</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6158</v>
+        <v>-0.6207</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-1.4024</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.9644</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.4381</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9737</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1684</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.1421</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.7379</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.8657</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.8721</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.1695</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.449</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2443</v>
+        <v>0.6158</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9013</v>
+        <v>0.6158</v>
       </c>
       <c r="F22" t="n">
-        <v>2.657</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8461</v>
+        <v>0.6158</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0842</v>
+        <v>0.6158</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9303</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8051</v>
+        <v>0.6158</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5567</v>
+        <v>0.6158</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3618</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4725</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4315</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3368</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1683</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7854</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3829</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1656</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.2008</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3668</v>
+        <v>-0.4286</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2554</v>
@@ -2248,13 +2248,13 @@
         <v>0.7789</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2997</v>
+        <v>0.2365</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3618</v>
+        <v>0.2363</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0621</v>
+        <v>0.0002</v>
       </c>
       <c r="V23" t="n">
         <v>0.6105</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2728</v>
+        <v>-1.399</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3447</v>
+        <v>-2.8463</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0719</v>
+        <v>1.4473</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5212</v>
@@ -2326,13 +2326,13 @@
         <v>1.9474</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1627</v>
+        <v>1.0364</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5999</v>
+        <v>-0.1015</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7626</v>
+        <v>1.1379</v>
       </c>
       <c r="V24" t="n">
         <v>0.2279</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9643</v>
+        <v>-1.7811</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3844</v>
+        <v>-0.2847</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5799</v>
+        <v>-1.4964</v>
       </c>
       <c r="G25" t="n">
         <v>-2.666</v>
@@ -2404,13 +2404,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3122</v>
+        <v>0.4954</v>
       </c>
       <c r="T25" t="n">
-        <v>0.108</v>
+        <v>0.2077</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2042</v>
+        <v>0.2877</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.0111</v>
+        <v>-5.6439</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.2016</v>
+        <v>-6.3013</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1906</v>
+        <v>0.6574</v>
       </c>
       <c r="G26" t="n">
         <v>-4.7035</v>
@@ -2482,13 +2482,13 @@
         <v>1.5579</v>
       </c>
       <c r="S26" t="n">
-        <v>0.003</v>
+        <v>0.3701</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1301</v>
+        <v>-0.2298</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1331</v>
+        <v>0.5999</v>
       </c>
       <c r="V26" t="n">
         <v>1.2211</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>7.5018</v>
+        <v>10.16</v>
       </c>
       <c r="E27" t="n">
-        <v>2.802200000000002</v>
+        <v>2.802400000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>4.699499999999999</v>
+        <v>7.357799999999998</v>
       </c>
       <c r="G27" t="n">
-        <v>0.158199999999999</v>
+        <v>0.1582000000000008</v>
       </c>
       <c r="H27" t="n">
         <v>-2.5326</v>
       </c>
       <c r="I27" t="n">
-        <v>2.690999999999999</v>
+        <v>2.690999999999998</v>
       </c>
       <c r="J27" t="n">
         <v>12.1567</v>
@@ -2539,16 +2539,16 @@
         <v>4.519100000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>7.637600000000003</v>
+        <v>7.637600000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-11.9984</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.051800000000001</v>
+        <v>-7.0518</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.946599999999999</v>
+        <v>-4.9466</v>
       </c>
       <c r="P27" t="n">
         <v>-7.7895</v>
@@ -2560,13 +2560,13 @@
         <v>14.6052</v>
       </c>
       <c r="S27" t="n">
-        <v>5.0853</v>
+        <v>7.743300000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>2.639800000000001</v>
+        <v>2.6397</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4456</v>
+        <v>5.1036</v>
       </c>
       <c r="V27" t="n">
         <v>10.048</v>
